--- a/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,17; 54,3</t>
+          <t>28,42; 56,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,14; 53,83</t>
+          <t>24,33; 52,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 57,0</t>
+          <t>21,15; 56,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 59,98</t>
+          <t>31,45; 59,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 74,53</t>
+          <t>43,85; 73,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 36,61</t>
+          <t>9,93; 35,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,93; 55,0</t>
+          <t>33,72; 54,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 60,28</t>
+          <t>38,93; 60,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 40,04</t>
+          <t>19,05; 41,05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,3; 49,94</t>
+          <t>31,39; 49,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,34; 50,99</t>
+          <t>32,54; 51,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 44,22</t>
+          <t>5,87; 46,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,77; 59,64</t>
+          <t>41,14; 58,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,77; 62,32</t>
+          <t>43,98; 62,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,89; 62,04</t>
+          <t>24,38; 59,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,18; 52,44</t>
+          <t>39,1; 52,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,56; 54,83</t>
+          <t>41,16; 54,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 44,55</t>
+          <t>13,0; 43,35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,81; 66,07</t>
+          <t>43,25; 67,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,49; 42,47</t>
+          <t>22,66; 43,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 40,61</t>
+          <t>11,89; 42,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,06; 64,36</t>
+          <t>41,06; 63,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 47,78</t>
+          <t>27,4; 48,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,5; 67,14</t>
+          <t>37,13; 69,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,97; 62,42</t>
+          <t>44,87; 62,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 42,19</t>
+          <t>27,28; 42,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,83; 50,43</t>
+          <t>28,18; 51,32</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,14; 50,61</t>
+          <t>27,07; 50,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 52,14</t>
+          <t>24,74; 50,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 45,73</t>
+          <t>9,05; 46,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,51; 66,79</t>
+          <t>44,34; 68,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,59; 60,61</t>
+          <t>34,84; 61,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,1; 85,65</t>
+          <t>26,05; 84,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,15; 55,61</t>
+          <t>39,1; 55,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 53,33</t>
+          <t>33,6; 52,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,02; 57,62</t>
+          <t>23,79; 57,17</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,18; 67,37</t>
+          <t>32,25; 64,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 44,12</t>
+          <t>16,43; 42,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,45; 58,78</t>
+          <t>28,99; 58,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,55; 70,65</t>
+          <t>40,49; 71,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 50,69</t>
+          <t>24,59; 50,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,94; 65,27</t>
+          <t>33,64; 64,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,25; 63,61</t>
+          <t>41,28; 63,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 44,24</t>
+          <t>24,01; 43,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,44; 57,92</t>
+          <t>36,09; 58,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,57; 54,91</t>
+          <t>31,55; 55,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,99; 43,45</t>
+          <t>19,64; 42,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 35,5</t>
+          <t>4,33; 34,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,17; 51,68</t>
+          <t>27,52; 52,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,58; 60,88</t>
+          <t>36,87; 61,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,24; 50,9</t>
+          <t>18,73; 51,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,09; 50,44</t>
+          <t>33,57; 50,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,53; 48,22</t>
+          <t>31,62; 48,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 39,52</t>
+          <t>17,07; 39,74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,94; 47,96</t>
+          <t>31,98; 47,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,86; 32,57</t>
+          <t>18,67; 33,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,02; 50,07</t>
+          <t>24,07; 50,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,36; 65,57</t>
+          <t>49,42; 65,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,39; 42,0</t>
+          <t>27,31; 42,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,97; 57,0</t>
+          <t>35,38; 58,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,4; 54,62</t>
+          <t>43,34; 54,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,76</t>
+          <t>25,57; 35,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,18; 49,91</t>
+          <t>34,36; 51,0</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,27; 58,45</t>
+          <t>44,46; 59,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,16; 47,89</t>
+          <t>34,06; 47,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,79; 32,65</t>
+          <t>12,56; 31,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,16; 65,23</t>
+          <t>50,09; 64,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,12; 58,28</t>
+          <t>42,27; 56,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,45; 48,97</t>
+          <t>29,74; 50,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,36; 59,83</t>
+          <t>49,25; 60,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,7; 51,0</t>
+          <t>40,4; 50,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,35; 39,8</t>
+          <t>25,44; 39,68</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41,41; 48,75</t>
+          <t>41,02; 48,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,04</t>
+          <t>31,4; 38,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,15; 34,05</t>
+          <t>19,62; 34,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50,18; 57,6</t>
+          <t>50,0; 57,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,91; 48,97</t>
+          <t>41,6; 48,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,95; 46,67</t>
+          <t>36,08; 46,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,0; 51,97</t>
+          <t>46,8; 51,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,87</t>
+          <t>37,96; 42,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,29; 39,01</t>
+          <t>29,76; 39,25</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10129</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17267</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7688</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29771</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>28904</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>17817</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9043; 18046</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7219; 15637</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5888; 15856</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11294; 21326</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12591; 21236</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3524; 12623</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22839; 36829</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>22729; 35307</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12066; 25998</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30227</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32249</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14675</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40932</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42685</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18431</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71159</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>74934</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>33106</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>23250; 37015</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25165; 39657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3801; 30111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>33435; 47739</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>34875; 49415</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11399; 27586</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>60738; 80909</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>64478; 85520</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>14491; 48332</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>28169</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17756</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5284</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27592</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21836</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12805</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>55761</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>39592</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18088</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>22013; 34121</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12689; 24538</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2561; 9093</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21603; 33502</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16139; 28456</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9138; 16983</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>46447; 64537</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>31343; 48368</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13003; 23682</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>19996</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13077</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31076</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20988</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7759</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51072</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34065</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11641</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13948; 25770</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8555; 17622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1507; 7720</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24939; 38246</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15236; 27012</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3352; 10877</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>42133; 59949</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>26310; 41346</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7024; 16878</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13050</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9079</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16923</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12926</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29972</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>22026</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>8624; 17339</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5260; 13604</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6087; 12257</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12164; 21417</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8627; 17720</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8358; 15961</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23438; 35959</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16111; 29003</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>16543; 26632</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>19166</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14055</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16328</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23567</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8595</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35493</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>37622</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>11048</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>13899; 24262</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9006; 19603</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>666; 5366</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11467; 21672</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>17889; 29964</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4669; 12897</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>28781; 43107</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>29843; 45729</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>6879; 16013</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>41330</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23871</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17296</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36958</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31555</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>102579</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>60830</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>48851</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>33292; 49382</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17617; 31669</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11476; 23969</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>51817; 68823</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>28886; 45087</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>24394; 40141</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>90569; 114088</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>51183; 71780</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>40079; 59484</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>60371</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>47741</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10676</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>70251</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>61574</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>30685</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>130622</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>109315</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>41361</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>52213; 69586</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39978; 56125</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6290; 15977</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>60424; 78293</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>52492; 70635</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>23163; 39003</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>117262; 143091</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>97581; 122273</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>32545; 50771</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>225514</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>169486</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>73475</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>129860</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>506430</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>407287</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>203335</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>205390; 243812</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>152963; 186468</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>51965; 90986</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>261595; 299338</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>218058; 256355</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>114136; 147287</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>479173; 530908</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>383953; 434542</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>172988; 228107</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,42; 56,71</t>
+          <t>27,3; 54,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,33; 52,69</t>
+          <t>24,77; 53,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 56,95</t>
+          <t>20,0; 56,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,45; 59,38</t>
+          <t>32,8; 60,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,85; 73,96</t>
+          <t>44,19; 75,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 35,57</t>
+          <t>11,13; 37,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 54,38</t>
+          <t>33,76; 53,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,93; 60,47</t>
+          <t>38,58; 60,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 41,05</t>
+          <t>17,89; 41,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,39; 49,97</t>
+          <t>30,94; 49,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 51,28</t>
+          <t>32,68; 50,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 46,52</t>
+          <t>6,21; 45,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,14; 58,74</t>
+          <t>41,69; 58,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,98; 62,31</t>
+          <t>44,55; 62,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,38; 59,01</t>
+          <t>25,54; 59,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,1; 52,08</t>
+          <t>40,16; 52,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,16; 54,6</t>
+          <t>41,06; 53,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,0; 43,35</t>
+          <t>11,73; 44,02</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,25; 67,04</t>
+          <t>44,47; 68,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,66; 43,82</t>
+          <t>21,01; 43,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 42,23</t>
+          <t>11,91; 39,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,06; 63,67</t>
+          <t>41,4; 63,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,4; 48,31</t>
+          <t>27,46; 48,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,13; 69,01</t>
+          <t>36,6; 67,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,87; 62,35</t>
+          <t>45,43; 61,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,28; 42,1</t>
+          <t>26,96; 42,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,18; 51,32</t>
+          <t>28,52; 51,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,07; 50,01</t>
+          <t>28,43; 51,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,74; 50,96</t>
+          <t>23,89; 50,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 46,36</t>
+          <t>8,77; 47,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,34; 68,0</t>
+          <t>44,03; 66,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,84; 61,77</t>
+          <t>35,14; 61,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 84,52</t>
+          <t>31,81; 86,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,1; 55,63</t>
+          <t>37,91; 54,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,6; 52,8</t>
+          <t>33,77; 52,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 57,17</t>
+          <t>24,51; 58,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,25; 64,84</t>
+          <t>31,31; 64,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 42,49</t>
+          <t>17,06; 43,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,99; 58,38</t>
+          <t>28,19; 58,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,49; 71,29</t>
+          <t>40,45; 70,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,59; 50,51</t>
+          <t>22,67; 51,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,64; 64,24</t>
+          <t>34,21; 65,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,28; 63,33</t>
+          <t>41,32; 63,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,01; 43,22</t>
+          <t>23,55; 42,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,09; 58,1</t>
+          <t>36,34; 57,27</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,55; 55,07</t>
+          <t>31,41; 56,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 42,75</t>
+          <t>19,67; 43,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 34,94</t>
+          <t>4,38; 33,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,52; 52,01</t>
+          <t>27,2; 51,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,87; 61,75</t>
+          <t>36,15; 61,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,73; 51,72</t>
+          <t>18,13; 51,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,57; 50,28</t>
+          <t>32,44; 49,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,62; 48,45</t>
+          <t>31,85; 48,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,07; 39,74</t>
+          <t>17,19; 39,23</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,98; 47,43</t>
+          <t>31,98; 48,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,67; 33,56</t>
+          <t>19,01; 32,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,07; 50,26</t>
+          <t>23,96; 50,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,42; 65,64</t>
+          <t>49,94; 66,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,31; 42,63</t>
+          <t>27,38; 42,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,38; 58,22</t>
+          <t>34,6; 56,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,34; 54,6</t>
+          <t>43,52; 54,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,57; 35,87</t>
+          <t>25,58; 36,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,36; 51,0</t>
+          <t>33,7; 50,02</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,46; 59,25</t>
+          <t>43,85; 59,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,06; 47,82</t>
+          <t>33,53; 47,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,56; 31,91</t>
+          <t>13,11; 31,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,09; 64,9</t>
+          <t>50,9; 65,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,27; 56,87</t>
+          <t>42,43; 56,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,74; 50,08</t>
+          <t>30,67; 51,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,25; 60,1</t>
+          <t>49,32; 59,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,4; 50,62</t>
+          <t>39,79; 50,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,44; 39,68</t>
+          <t>25,13; 39,83</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41,02; 48,7</t>
+          <t>41,87; 48,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,27</t>
+          <t>31,07; 38,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,62; 34,35</t>
+          <t>20,21; 33,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50,0; 57,21</t>
+          <t>50,03; 57,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,6; 48,9</t>
+          <t>41,9; 49,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,56</t>
+          <t>35,56; 46,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,8; 51,85</t>
+          <t>46,91; 52,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,96</t>
+          <t>37,74; 42,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,76; 39,25</t>
+          <t>29,45; 39,19</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9043; 18046</t>
+          <t>8685; 17463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7219; 15637</t>
+          <t>7352; 15798</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5888; 15856</t>
+          <t>5568; 15791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11294; 21326</t>
+          <t>11778; 21775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12591; 21236</t>
+          <t>12687; 21534</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3524; 12623</t>
+          <t>3951; 13199</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22839; 36829</t>
+          <t>22864; 36206</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22729; 35307</t>
+          <t>22529; 35407</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12066; 25998</t>
+          <t>11331; 26154</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23250; 37015</t>
+          <t>22919; 36975</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25165; 39657</t>
+          <t>25275; 39421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3801; 30111</t>
+          <t>4021; 29662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33435; 47739</t>
+          <t>33884; 47698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34875; 49415</t>
+          <t>35326; 49615</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11399; 27586</t>
+          <t>11942; 27953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60738; 80909</t>
+          <t>62391; 82088</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64478; 85520</t>
+          <t>64317; 83869</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14491; 48332</t>
+          <t>13075; 49076</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22013; 34121</t>
+          <t>22634; 34934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12689; 24538</t>
+          <t>11764; 24096</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2561; 9093</t>
+          <t>2565; 8519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21603; 33502</t>
+          <t>21783; 33361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16139; 28456</t>
+          <t>16174; 28290</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9138; 16983</t>
+          <t>9007; 16640</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46447; 64537</t>
+          <t>47023; 63650</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31343; 48368</t>
+          <t>30975; 49149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13003; 23682</t>
+          <t>13159; 23680</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13948; 25770</t>
+          <t>14650; 26427</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8555; 17622</t>
+          <t>8260; 17443</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1507; 7720</t>
+          <t>1460; 7867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24939; 38246</t>
+          <t>24764; 37588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15236; 27012</t>
+          <t>15369; 26747</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3352; 10877</t>
+          <t>4094; 11136</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42133; 59949</t>
+          <t>40852; 59132</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26310; 41346</t>
+          <t>26447; 40823</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7024; 16878</t>
+          <t>7235; 17190</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8624; 17339</t>
+          <t>8372; 17259</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5260; 13604</t>
+          <t>5462; 13906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6087; 12257</t>
+          <t>5918; 12197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12164; 21417</t>
+          <t>12151; 21174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8627; 17720</t>
+          <t>7955; 18145</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8358; 15961</t>
+          <t>8499; 16163</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23438; 35959</t>
+          <t>23464; 36152</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16111; 29003</t>
+          <t>15800; 28396</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16543; 26632</t>
+          <t>16659; 26252</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13899; 24262</t>
+          <t>13837; 24840</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9006; 19603</t>
+          <t>9019; 19841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>666; 5366</t>
+          <t>673; 5091</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11467; 21672</t>
+          <t>11336; 21592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17889; 29964</t>
+          <t>17541; 29922</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4669; 12897</t>
+          <t>4522; 12835</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28781; 43107</t>
+          <t>27806; 42556</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29843; 45729</t>
+          <t>30058; 45325</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6879; 16013</t>
+          <t>6927; 15806</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33292; 49382</t>
+          <t>33291; 50089</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17617; 31669</t>
+          <t>17939; 31108</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11476; 23969</t>
+          <t>11425; 24288</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51817; 68823</t>
+          <t>52363; 69719</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28886; 45087</t>
+          <t>28957; 45188</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24394; 40141</t>
+          <t>23856; 39223</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90569; 114088</t>
+          <t>90933; 114064</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>51183; 71780</t>
+          <t>51200; 72907</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40079; 59484</t>
+          <t>39308; 58346</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52213; 69586</t>
+          <t>51507; 69702</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>39978; 56125</t>
+          <t>39359; 55898</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6290; 15977</t>
+          <t>6566; 15721</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60424; 78293</t>
+          <t>61402; 78500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52492; 70635</t>
+          <t>52697; 70340</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23163; 39003</t>
+          <t>23887; 39893</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>117262; 143091</t>
+          <t>117428; 142654</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>97581; 122273</t>
+          <t>96110; 121597</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32545; 50771</t>
+          <t>32157; 50966</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>205390; 243812</t>
+          <t>209635; 244360</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>152963; 186468</t>
+          <t>151353; 186167</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51965; 90986</t>
+          <t>53537; 89794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>261595; 299338</t>
+          <t>261767; 299156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>218058; 256355</t>
+          <t>219625; 259167</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>114136; 147287</t>
+          <t>112479; 147517</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>479173; 530908</t>
+          <t>480298; 536733</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>383953; 434542</t>
+          <t>381664; 432825</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>172988; 228107</t>
+          <t>171148; 227743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>41,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>39,21%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 54,88</t>
+          <t>32,06; 59,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,77; 53,23</t>
+          <t>44,14; 74,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,0; 56,71</t>
+          <t>12,02; 37,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,8; 60,63</t>
+          <t>28,17; 54,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,19; 75,0</t>
+          <t>26,14; 53,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 37,19</t>
+          <t>18,52; 47,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,76; 53,46</t>
+          <t>34,93; 55,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,58; 60,64</t>
+          <t>38,7; 60,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 41,29</t>
+          <t>17,47; 36,79</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>40,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>41,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>53,83%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,94; 49,92</t>
+          <t>41,77; 59,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,68; 50,97</t>
+          <t>44,77; 62,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 45,82</t>
+          <t>24,99; 60,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,69; 58,69</t>
+          <t>32,3; 49,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,55; 62,56</t>
+          <t>32,34; 50,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,54; 59,79</t>
+          <t>19,25; 45,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,16; 52,84</t>
+          <t>39,18; 52,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,06; 53,54</t>
+          <t>41,56; 54,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 44,02</t>
+          <t>24,94; 48,61</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52,44%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>55,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>31,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24,54%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,44%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,47; 68,64</t>
+          <t>41,06; 64,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,01; 43,03</t>
+          <t>26,16; 47,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 39,56</t>
+          <t>36,03; 67,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,4; 63,41</t>
+          <t>42,81; 66,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,46; 48,03</t>
+          <t>21,49; 42,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,6; 67,62</t>
+          <t>13,11; 40,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,43; 61,49</t>
+          <t>45,97; 62,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,96; 42,78</t>
+          <t>27,13; 42,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,52; 51,32</t>
+          <t>28,09; 50,46</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47,99%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>38,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>37,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,99%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,43; 51,29</t>
+          <t>44,51; 66,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,89; 50,44</t>
+          <t>34,59; 60,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 47,25</t>
+          <t>23,96; 85,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,03; 66,83</t>
+          <t>28,14; 50,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,14; 61,16</t>
+          <t>25,63; 52,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,81; 86,53</t>
+          <t>6,35; 46,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,91; 54,87</t>
+          <t>39,15; 55,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,77; 52,13</t>
+          <t>34,62; 53,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,51; 58,23</t>
+          <t>21,98; 56,61</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56,33%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>48,8%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>28,42%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43,25%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,31; 64,55</t>
+          <t>40,55; 70,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 43,43</t>
+          <t>22,85; 50,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,19; 58,1</t>
+          <t>33,94; 66,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,45; 70,48</t>
+          <t>32,18; 67,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 51,72</t>
+          <t>17,15; 44,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,21; 65,06</t>
+          <t>27,7; 58,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,32; 63,67</t>
+          <t>42,25; 63,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,55; 42,31</t>
+          <t>24,08; 44,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,34; 57,27</t>
+          <t>36,43; 57,62</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48,57%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33,22%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>43,5%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>30,65%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48,57%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,41; 56,39</t>
+          <t>27,17; 51,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,67; 43,27</t>
+          <t>36,58; 60,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 33,15</t>
+          <t>19,36; 49,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,2; 51,82</t>
+          <t>31,57; 54,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,15; 61,66</t>
+          <t>19,99; 43,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,13; 51,48</t>
+          <t>4,04; 34,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,44; 49,64</t>
+          <t>33,09; 50,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,85; 48,02</t>
+          <t>31,53; 48,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 39,23</t>
+          <t>15,58; 38,28</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58,42%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34,94%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45,28%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>39,7%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>25,3%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36,27%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58,42%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,98; 48,11</t>
+          <t>50,36; 65,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,01; 32,97</t>
+          <t>27,39; 42,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,96; 50,93</t>
+          <t>34,91; 56,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,94; 66,5</t>
+          <t>31,94; 47,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,38; 42,72</t>
+          <t>18,86; 32,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,6; 56,88</t>
+          <t>21,19; 44,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,52; 54,59</t>
+          <t>43,4; 54,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 36,43</t>
+          <t>25,2; 35,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,7; 50,02</t>
+          <t>31,32; 47,43</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>49,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>51,4%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>40,68%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>58,24%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>49,58%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,85; 59,35</t>
+          <t>51,16; 65,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,53; 47,63</t>
+          <t>43,12; 58,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,11; 31,4</t>
+          <t>28,87; 48,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,9; 65,08</t>
+          <t>43,27; 58,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,43; 56,64</t>
+          <t>34,16; 47,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,67; 51,22</t>
+          <t>11,79; 31,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,32; 59,92</t>
+          <t>49,36; 59,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,79; 50,34</t>
+          <t>40,7; 51,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,13; 39,83</t>
+          <t>24,64; 38,87</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>45,04%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41,87; 48,81</t>
+          <t>50,18; 57,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,07; 38,21</t>
+          <t>41,91; 48,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,21; 33,9</t>
+          <t>35,96; 46,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50,03; 57,17</t>
+          <t>41,41; 48,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,9; 49,44</t>
+          <t>31,35; 38,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,56; 46,63</t>
+          <t>23,22; 33,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,91; 52,42</t>
+          <t>47,0; 51,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,74; 42,79</t>
+          <t>37,67; 42,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,45; 39,19</t>
+          <t>31,5; 39,14</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17267</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>13205</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>11637</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10129</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16566</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17267</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>13344</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8685; 17463</t>
+          <t>11514; 21540</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7352; 15798</t>
+          <t>12674; 21398</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5568; 15791</t>
+          <t>3271; 10080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11778; 21775</t>
+          <t>8962; 17279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12687; 21534</t>
+          <t>7757; 15976</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3951; 13199</t>
+          <t>4349; 11220</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22864; 36206</t>
+          <t>23660; 37253</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22529; 35407</t>
+          <t>22598; 35199</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11331; 26154</t>
+          <t>8854; 18652</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40932</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42685</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16281</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>30227</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>32249</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14675</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40932</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42685</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>28257</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22919; 36975</t>
+          <t>33945; 48475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25275; 39421</t>
+          <t>35504; 49419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4021; 29662</t>
+          <t>10471; 25465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33884; 47698</t>
+          <t>23926; 36994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35326; 49615</t>
+          <t>25009; 39435</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11942; 27953</t>
+          <t>7334; 17479</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62391; 82088</t>
+          <t>60867; 81473</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64317; 83869</t>
+          <t>65103; 85884</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13075; 49076</t>
+          <t>19956; 38890</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27592</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11432</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>28169</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>17756</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5284</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27592</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21836</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>16818</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22634; 34934</t>
+          <t>21604; 33866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11764; 24096</t>
+          <t>15406; 28142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2565; 8519</t>
+          <t>7871; 14794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21783; 33361</t>
+          <t>21789; 33627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16174; 28290</t>
+          <t>12035; 23782</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9007; 16640</t>
+          <t>2805; 8765</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47023; 63650</t>
+          <t>47584; 64607</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30975; 49149</t>
+          <t>31171; 48476</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13159; 23680</t>
+          <t>12144; 21816</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31076</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20988</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7028</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19996</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13077</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3882</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31076</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20988</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11065</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14650; 26427</t>
+          <t>25035; 37566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8260; 17443</t>
+          <t>15126; 26506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1460; 7867</t>
+          <t>2841; 10194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24764; 37588</t>
+          <t>14497; 26077</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15369; 26747</t>
+          <t>8861; 18029</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4094; 11136</t>
+          <t>1084; 8024</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40852; 59132</t>
+          <t>42188; 59928</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26447; 40823</t>
+          <t>27114; 41764</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7235; 17190</t>
+          <t>6359; 16377</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16923</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12926</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12564</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>13050</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>9100</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9079</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16923</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12926</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21854</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8372; 17259</t>
+          <t>12182; 21226</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5462; 13906</t>
+          <t>8018; 17784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5918; 12197</t>
+          <t>8535; 16631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12151; 21174</t>
+          <t>8605; 18015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7955; 18145</t>
+          <t>5492; 14128</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8499; 16163</t>
+          <t>6009; 12608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23464; 36152</t>
+          <t>23991; 36122</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15800; 28396</t>
+          <t>16161; 29686</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16659; 26252</t>
+          <t>17062; 26988</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16328</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23567</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>19166</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>14055</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16328</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>23567</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>9931</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13837; 24840</t>
+          <t>11321; 21538</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9019; 19841</t>
+          <t>17750; 29542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>673; 5091</t>
+          <t>4333; 11167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11336; 21592</t>
+          <t>13908; 24191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17541; 29922</t>
+          <t>9167; 19925</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4522; 12835</t>
+          <t>638; 5517</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27806; 42556</t>
+          <t>28364; 43237</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30058; 45325</t>
+          <t>29755; 45515</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6927; 15806</t>
+          <t>5948; 14615</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>36958</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>29581</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>41330</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>23871</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>17296</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>61249</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>36958</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31555</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48851</t>
+          <t>44620</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33291; 50089</t>
+          <t>52798; 68741</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17939; 31108</t>
+          <t>28973; 44420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11425; 24288</t>
+          <t>22807; 36842</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52363; 69719</t>
+          <t>33249; 49928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28957; 45188</t>
+          <t>17800; 30733</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23856; 39223</t>
+          <t>9839; 20768</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90933; 114064</t>
+          <t>90677; 114133</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>51200; 72907</t>
+          <t>50429; 71562</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39308; 58346</t>
+          <t>35002; 53006</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>70251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>61574</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31027</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>60371</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>47741</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>10676</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>70251</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>61574</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30685</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>41530</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51507; 69702</t>
+          <t>61718; 78682</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>39359; 55898</t>
+          <t>53551; 72383</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6566; 15721</t>
+          <t>22990; 38685</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61402; 78500</t>
+          <t>50816; 68650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52697; 70340</t>
+          <t>40097; 56206</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23887; 39893</t>
+          <t>6163; 16362</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>117428; 142654</t>
+          <t>117507; 142448</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>96110; 121597</t>
+          <t>98306; 123207</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32157; 50966</t>
+          <t>32504; 51263</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>121338</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>225514</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>169486</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>73475</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>280916</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>237801</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>187419</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>209635; 244360</t>
+          <t>262560; 301398</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>151353; 186167</t>
+          <t>219700; 256707</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53537; 89794</t>
+          <t>106201; 137074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>261767; 299156</t>
+          <t>207320; 244101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>219625; 259167</t>
+          <t>152738; 185334</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>112479; 147517</t>
+          <t>54849; 78050</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>480298; 536733</t>
+          <t>481200; 532083</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>381664; 432825</t>
+          <t>380987; 433598</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>171148; 227743</t>
+          <t>167434; 208024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Provincia-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.4612795032128404</v>
+        <v>0.4722952555714748</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.6014051133347678</v>
+        <v>0.5038681631579041</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.2201018200568543</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.4150075702086364</v>
+        <v>0.4361174503586625</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.3920979648385204</v>
+        <v>0.3488890066472408</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.3131996545806865</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.4395422471388949</v>
+        <v>0.4556109464731452</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.4950181309602348</v>
+        <v>0.4298881746763392</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0.2632190012075195</v>
@@ -667,28 +667,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3206187475257563</v>
+        <v>0.3620667884427706</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.4414294145813135</v>
+        <v>0.3824151309727361</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.1201886825232232</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2816535332917799</v>
+        <v>0.3142053165494396</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.2613710024826029</v>
+        <v>0.2450536212237205</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.1852202503521532</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.3493244512298525</v>
+        <v>0.3675660541829899</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.3870193879008262</v>
+        <v>0.3490704960211852</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0.1746590533006892</v>
@@ -702,28 +702,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.5997887693352357</v>
+        <v>0.5928000859434656</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.7453027448281438</v>
+        <v>0.6125892627662518</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.3703713149208114</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.543043996044576</v>
+        <v>0.5461057107573494</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.5383107570656324</v>
+        <v>0.4701368254333086</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.4779046059169321</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5500188948178931</v>
+        <v>0.5332772012998677</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.6028193733353759</v>
+        <v>0.5084528428363834</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0.3679243221758442</v>
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5036244304466816</v>
+        <v>0.491007065732988</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.5382569652458234</v>
+        <v>0.4979558781208919</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.3885552708723573</v>
+        <v>0.3797492021531617</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.408057725170147</v>
+        <v>0.4320889327694836</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.4170018156258632</v>
+        <v>0.437756607468934</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.3142620634521427</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.4580555470669411</v>
+        <v>0.4629533984256314</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.4783907122377126</v>
+        <v>0.4694811989109924</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.3531709933182587</v>
+        <v>0.3489333166564085</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.4176595977068927</v>
+        <v>0.4087430987615043</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.4477107789206107</v>
+        <v>0.4188509188634996</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2498908289675678</v>
+        <v>0.2420204483878191</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.322996468350061</v>
+        <v>0.3442237334362889</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.3233816914243586</v>
+        <v>0.353105082344024</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0.1924554559390502</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.3918057414148061</v>
+        <v>0.4056654177790158</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.4156286343593442</v>
+        <v>0.4112315615368583</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.2494269429745898</v>
+        <v>0.2499490229367891</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.5964336859113883</v>
+        <v>0.5709493518761287</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.6231727849916974</v>
+        <v>0.5767128669569634</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.6077256320397243</v>
+        <v>0.5669312983890803</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.4994048491779128</v>
+        <v>0.5207462459031099</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.5099296679535558</v>
+        <v>0.5222767055463395</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0.4586986742917378</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5244461180650692</v>
+        <v>0.5252019639097362</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.5482974219860421</v>
+        <v>0.5275293472699424</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.486074204910388</v>
+        <v>0.478826094915199</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.524396333260804</v>
+        <v>0.5160022930326313</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.3707423762256977</v>
+        <v>0.3582469424288311</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.523340583583852</v>
+        <v>0.5412239852738825</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.5534837931667934</v>
+        <v>0.5178646491574784</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.317086248579467</v>
+        <v>0.312845210000638</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.2518165660850052</v>
+        <v>0.2378733483431449</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.5386979991512685</v>
+        <v>0.5169208814928512</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.3445919455768914</v>
+        <v>0.3363555532448376</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.3890139493953104</v>
+        <v>0.3945646887885125</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4106061651640907</v>
+        <v>0.4049208209204359</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.2615755516962056</v>
+        <v>0.2590941799668749</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3603290937150528</v>
+        <v>0.3891150036768607</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.4281206889118948</v>
+        <v>0.397095166574539</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2149231833955695</v>
+        <v>0.2175484725475255</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.1311488071565436</v>
+        <v>0.1034470314717936</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.4597064837745383</v>
+        <v>0.4314143219126282</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.2712960484273413</v>
+        <v>0.2686007372737053</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.2808999015526302</v>
+        <v>0.2920661029049856</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.6436400058085306</v>
+        <v>0.6151652247051465</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.4778137763637623</v>
+        <v>0.4660864857772939</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.6772032168133982</v>
+        <v>0.7018504155495663</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.6607271144915651</v>
+        <v>0.6182265381086729</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4247019808937464</v>
+        <v>0.4376813520705679</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.4098515532524536</v>
+        <v>0.3842704408961463</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.6241610115453644</v>
+        <v>0.586055017404283</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.4219119531189583</v>
+        <v>0.4107231803145353</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.504634459810175</v>
+        <v>0.4972036084732419</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5525187038294651</v>
+        <v>0.551741589565084</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.4799315775187655</v>
+        <v>0.5023048047176664</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.5927342931348584</v>
+        <v>0.6464594785784372</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.3880922585261118</v>
+        <v>0.3513104310695965</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.3781711730499282</v>
+        <v>0.3493209765359598</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.2364170630599007</v>
+        <v>0.2301211553152227</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.4739054843451959</v>
+        <v>0.4571623170991999</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.434997818482946</v>
+        <v>0.4316927122852053</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.3824507614152971</v>
+        <v>0.4216226228032314</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.4451082532031457</v>
+        <v>0.4446755577949175</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.3458922828201666</v>
+        <v>0.3859242223467234</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.2395764106278752</v>
+        <v>0.33982458237247</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2813509077373829</v>
+        <v>0.255578277979367</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.2562544811785605</v>
+        <v>0.250210444072314</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.06349885589707677</v>
+        <v>0.07826802943985883</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.3914714436407796</v>
+        <v>0.3875094226603834</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.3462396171963531</v>
+        <v>0.3488956651182488</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.2197839209038556</v>
+        <v>0.2666272587083128</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.667913100075931</v>
+        <v>0.6434719453400058</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.6061100460283197</v>
+        <v>0.6113708275772135</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.8597067329791728</v>
+        <v>0.8500329868154666</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.5061132899433084</v>
+        <v>0.4563769766950463</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.5213883197571801</v>
+        <v>0.4583190462813571</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.4699399283781451</v>
+        <v>0.4562477808950461</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5560815310776955</v>
+        <v>0.5349970966295287</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.5333133991819685</v>
+        <v>0.5064914560438766</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.5660597545415883</v>
+        <v>0.6087129686058993</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.5632867490828281</v>
+        <v>0.4508436287513464</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.3684023834130568</v>
+        <v>0.3503481000284988</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.4996922021485824</v>
+        <v>0.5072310459098661</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.4880157311884761</v>
+        <v>0.494869922808184</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.2842135354362265</v>
+        <v>0.2771722735391469</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.4281991132716518</v>
+        <v>0.4305258952493708</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.5278406551120686</v>
+        <v>0.4731805039153537</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.3282318715392648</v>
+        <v>0.3141611866840263</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.466575811314276</v>
+        <v>0.47199205484873</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.4054806254752397</v>
+        <v>0.3076568333432102</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.2285369566398295</v>
+        <v>0.2363065158530887</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3394387691846157</v>
+        <v>0.3636752680197459</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3217850375214405</v>
+        <v>0.3565416382702931</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1715182363093706</v>
+        <v>0.1791162352793107</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.2769596433186809</v>
+        <v>0.2874328193794923</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.4225052058721836</v>
+        <v>0.3826815882171398</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.2408343893487853</v>
+        <v>0.226042640319123</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3642710332562639</v>
+        <v>0.3717753528316054</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.706512006368739</v>
+        <v>0.5675934358252114</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.5068653905655334</v>
+        <v>0.490605193915186</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.6614704939122135</v>
+        <v>0.6572770144223445</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.6737146902952583</v>
+        <v>0.6243625410451809</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.4412376708122193</v>
+        <v>0.4250488943662359</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.5810926357373938</v>
+        <v>0.5750874625435318</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.6361356689561104</v>
+        <v>0.5753764379605452</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.4423803210994726</v>
+        <v>0.4059349133242768</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.5761848208325321</v>
+        <v>0.5792824738271952</v>
       </c>
     </row>
     <row r="19">
@@ -1177,31 +1177,31 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.3918236574457624</v>
+        <v>0.4349233288329477</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.4856533844932558</v>
+        <v>0.4965438896359325</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.3321586734146271</v>
+        <v>0.3278479366884877</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.4350420523546132</v>
+        <v>0.4678465462018038</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.3064781294345037</v>
+        <v>0.296869662794448</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.1580603343755104</v>
+        <v>0.2088490466071727</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.4140335658462114</v>
+        <v>0.4510406139316008</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.3985970917134845</v>
+        <v>0.3990062923224929</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.2601338015792998</v>
+        <v>0.2781674939762943</v>
       </c>
     </row>
     <row r="20">
@@ -1212,31 +1212,31 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.2716809408270157</v>
+        <v>0.3153209800378932</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.3657778666729787</v>
+        <v>0.3731631388214218</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.1935789567007389</v>
+        <v>0.1830976096808144</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3156856496850026</v>
+        <v>0.3503931498939412</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.1998939883406824</v>
+        <v>0.2004386711646053</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.04039363200011917</v>
+        <v>0.07206936044490019</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.3308629201222468</v>
+        <v>0.3559379628374764</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.3152544063547626</v>
+        <v>0.3192798906623389</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.155814682991863</v>
+        <v>0.1762546472731229</v>
       </c>
     </row>
     <row r="21">
@@ -1247,31 +1247,31 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.5168452408577144</v>
+        <v>0.5564133849630158</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.6087901565603049</v>
+        <v>0.6150927535522343</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.4988995313705045</v>
+        <v>0.4966535511988642</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.549118718352628</v>
+        <v>0.5901649996259077</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.4344856334225071</v>
+        <v>0.4072026338362734</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.3493106713041059</v>
+        <v>0.3916816034579998</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.5043571773740811</v>
+        <v>0.5271138713332993</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.4822283089811034</v>
+        <v>0.4864427177492915</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.3828300790949566</v>
+        <v>0.3871319310022786</v>
       </c>
     </row>
     <row r="22">
@@ -1286,31 +1286,31 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.584200569214791</v>
+        <v>0.5624001477972072</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.3494170684607408</v>
+        <v>0.364149604665843</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.4527914429196261</v>
+        <v>0.4367783603850218</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.3969761595117522</v>
+        <v>0.4059530344023145</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.252976767825861</v>
+        <v>0.2564096861419342</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.3239682037046092</v>
+        <v>0.350814864495768</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.4909149819528746</v>
+        <v>0.4853478270515801</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.3039457816055118</v>
+        <v>0.3128098223452991</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.3992781814928715</v>
+        <v>0.4004063155371658</v>
       </c>
     </row>
     <row r="23">
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.5036001864474948</v>
+        <v>0.4867591143230816</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.2739258239854533</v>
+        <v>0.2972816544088168</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.3490978750413135</v>
+        <v>0.3337208487081185</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.3193576495699489</v>
+        <v>0.3368208811750535</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1886360788875847</v>
+        <v>0.1899700499149448</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.2119439298220803</v>
+        <v>0.2555738553896479</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.4339558561018683</v>
+        <v>0.4389510773369885</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.2519772393699843</v>
+        <v>0.2604378833608402</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.3132105554097923</v>
+        <v>0.3250902343883053</v>
       </c>
     </row>
     <row r="24">
@@ -1356,31 +1356,31 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.6556622390002919</v>
+        <v>0.6382670633063507</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.4199670680951707</v>
+        <v>0.4425378343795626</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.5639328260432511</v>
+        <v>0.5498920928993342</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.4795591070749122</v>
+        <v>0.4863950413948797</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.3256899752572781</v>
+        <v>0.330334311754435</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.4473672395000488</v>
+        <v>0.4766859145915652</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.546207604932421</v>
+        <v>0.5420190178900705</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.357573370681054</v>
+        <v>0.3602520040993659</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.4743163798639103</v>
+        <v>0.479715545511391</v>
       </c>
     </row>
     <row r="25">
@@ -1395,31 +1395,31 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.5823738072215981</v>
+        <v>0.5543852012649367</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.4957834412864573</v>
+        <v>0.4989810326789519</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.3895954479729838</v>
+        <v>0.3803241166502856</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.5140182526764392</v>
+        <v>0.4893349949007043</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.4067606549837836</v>
+        <v>0.3889397559445772</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.2009774947149787</v>
+        <v>0.2081276448290039</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.5486523225401284</v>
+        <v>0.5218581533889352</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.4525296584475371</v>
+        <v>0.4463909835320387</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.3148626340086576</v>
+        <v>0.3096426578730228</v>
       </c>
     </row>
     <row r="26">
@@ -1430,31 +1430,31 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.511638159903209</v>
+        <v>0.4850761422521752</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.4311819336732574</v>
+        <v>0.4353977212875535</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.2886759370503201</v>
+        <v>0.2863984158090953</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.4326633267526577</v>
+        <v>0.4222974978204725</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.3416331240820251</v>
+        <v>0.3239516494445678</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.1179379143031134</v>
+        <v>0.122705675240968</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.4935647460180483</v>
+        <v>0.4743152417103469</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.4069541428673786</v>
+        <v>0.3973322347147841</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.2464344942756952</v>
+        <v>0.2414675987037812</v>
       </c>
     </row>
     <row r="27">
@@ -1465,31 +1465,31 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.6522726137221292</v>
+        <v>0.6196164612111316</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.5828148096878443</v>
+        <v>0.5651263549065297</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.4857585277628243</v>
+        <v>0.4818823992368125</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.584501102198059</v>
+        <v>0.5585984966336142</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.4788759972133242</v>
+        <v>0.4611863900437492</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.3130827354598268</v>
+        <v>0.3039665487653543</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.5983246553601281</v>
+        <v>0.5727572142120235</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.5100371304099605</v>
+        <v>0.4929731893673696</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.388653772612761</v>
+        <v>0.377625410649333</v>
       </c>
     </row>
     <row r="28">
@@ -1504,31 +1504,31 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
     </row>
     <row r="29">
@@ -1539,31 +1539,31 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
     </row>
     <row r="30">
@@ -1574,31 +1574,31 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="31">
@@ -1653,7 +1653,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1753,28 +1753,28 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>22</v>
@@ -1788,28 +1788,28 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>16566</v>
+        <v>25349</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>17267</v>
+        <v>26858</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5990</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13205</v>
+        <v>20034</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>11637</v>
+        <v>16986</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>7353</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>29771</v>
+        <v>45383</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>28904</v>
+        <v>43844</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>13344</v>
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11514</v>
+        <v>19433</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>12674</v>
+        <v>20384</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3271</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8962</v>
+        <v>14434</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>7757</v>
+        <v>11930</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>4349</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>23660</v>
+        <v>36613</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>22598</v>
+        <v>35601</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>8854</v>
@@ -1858,28 +1858,28 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>21540</v>
+        <v>31817</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21398</v>
+        <v>32653</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>10080</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17279</v>
+        <v>25086</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>15976</v>
+        <v>22889</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>11220</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>37253</v>
+        <v>53119</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>35199</v>
+        <v>51857</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>18652</v>
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>16</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>34</v>
@@ -1932,28 +1932,28 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>40932</v>
+        <v>46765</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>42685</v>
+        <v>49287</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>16281</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>30227</v>
+        <v>37406</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>32249</v>
+        <v>38889</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>11975</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>71159</v>
+        <v>84171</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>74934</v>
+        <v>88176</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>28257</v>
@@ -1967,31 +1967,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>33945</v>
+        <v>38930</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>35504</v>
+        <v>41457</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>10471</v>
+        <v>10376</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>23926</v>
+        <v>29799</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>25009</v>
+        <v>31369</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>7334</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>60867</v>
+        <v>73755</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>65103</v>
+        <v>77236</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>19956</v>
+        <v>20241</v>
       </c>
     </row>
     <row r="11">
@@ -2002,31 +2002,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>48475</v>
+        <v>54379</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>49419</v>
+        <v>57082</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>25465</v>
+        <v>24306</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>36994</v>
+        <v>45080</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>39435</v>
+        <v>46398</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>17479</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>81473</v>
+        <v>95489</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>85884</v>
+        <v>99078</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>38890</v>
+        <v>38775</v>
       </c>
     </row>
     <row r="12">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>23</v>
@@ -2059,13 +2059,13 @@
         <v>9</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>53</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>27592</v>
+        <v>31080</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>21836</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>11432</v>
+        <v>13092</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>28169</v>
+        <v>30360</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>17756</v>
@@ -2094,13 +2094,13 @@
         <v>5386</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>55761</v>
+        <v>61441</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>39592</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>16818</v>
+        <v>18478</v>
       </c>
     </row>
     <row r="14">
@@ -2111,31 +2111,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>21604</v>
+        <v>24390</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>15406</v>
+        <v>15793</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7871</v>
+        <v>9413</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>21789</v>
+        <v>23280</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12035</v>
+        <v>12347</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2805</v>
+        <v>2342</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>47584</v>
+        <v>51278</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>31171</v>
+        <v>31616</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>12144</v>
+        <v>13678</v>
       </c>
     </row>
     <row r="15">
@@ -2146,31 +2146,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>33866</v>
+        <v>37053</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>28142</v>
+        <v>28409</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>14794</v>
+        <v>16978</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>33627</v>
+        <v>36244</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>23782</v>
+        <v>24841</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>8765</v>
+        <v>8700</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>64607</v>
+        <v>69658</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>48476</v>
+        <v>48345</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>21816</v>
+        <v>23285</v>
       </c>
     </row>
     <row r="16">
@@ -2185,31 +2185,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -2220,31 +2220,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>31076</v>
+        <v>38245</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20988</v>
+        <v>29460</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>7028</v>
+        <v>9659</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>19996</v>
+        <v>21758</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>13077</v>
+        <v>17562</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>4037</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>51072</v>
+        <v>60003</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>34065</v>
+        <v>47022</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>11065</v>
+        <v>13695</v>
       </c>
     </row>
     <row r="18">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>25035</v>
+        <v>30824</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15126</v>
+        <v>22634</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2841</v>
+        <v>5077</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14497</v>
+        <v>15829</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>8861</v>
+        <v>12580</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1084</v>
+        <v>1373</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>42188</v>
+        <v>50861</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>27114</v>
+        <v>38003</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>6359</v>
+        <v>8661</v>
       </c>
     </row>
     <row r="19">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>37566</v>
+        <v>44604</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>26506</v>
+        <v>35856</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>10194</v>
+        <v>12700</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>26077</v>
+        <v>28266</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>18029</v>
+        <v>23042</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>8024</v>
+        <v>8003</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>59928</v>
+        <v>70219</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>41764</v>
+        <v>55169</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>16377</v>
+        <v>19772</v>
       </c>
     </row>
     <row r="20">
@@ -2329,31 +2329,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -2364,31 +2364,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>16923</v>
+        <v>17729</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>12926</v>
+        <v>13526</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>12564</v>
+        <v>13582</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>13050</v>
+        <v>20041</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9100</v>
+        <v>10469</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>9291</v>
+        <v>9797</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>29972</v>
+        <v>37769</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>22026</v>
+        <v>23994</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>21854</v>
+        <v>23378</v>
       </c>
     </row>
     <row r="22">
@@ -2399,31 +2399,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>12182</v>
+        <v>12098</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>8018</v>
+        <v>9123</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8535</v>
+        <v>9738</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>8605</v>
+        <v>14439</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>5492</v>
+        <v>6765</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>6009</v>
+        <v>6541</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>23991</v>
+        <v>30546</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16161</v>
+        <v>17264</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>17062</v>
+        <v>18414</v>
       </c>
     </row>
     <row r="23">
@@ -2434,31 +2434,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>21226</v>
+        <v>22319</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>17784</v>
+        <v>18940</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>16631</v>
+        <v>17599</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18015</v>
+        <v>25285</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>14128</v>
+        <v>16054</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>12608</v>
+        <v>13086</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>36122</v>
+        <v>45927</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>29686</v>
+        <v>31003</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>26988</v>
+        <v>28692</v>
       </c>
     </row>
     <row r="24">
@@ -2473,31 +2473,31 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>21</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2508,31 +2508,31 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16328</v>
+        <v>21211</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>23567</v>
+        <v>24617</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>7435</v>
+        <v>8072</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>19166</v>
+        <v>21882</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>14055</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2496</v>
+        <v>3685</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>35493</v>
+        <v>43092</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>37622</v>
+        <v>38671</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>9931</v>
+        <v>11757</v>
       </c>
     </row>
     <row r="26">
@@ -2543,31 +2543,31 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11321</v>
+        <v>15378</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>17750</v>
+        <v>18500</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4333</v>
+        <v>4508</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>13908</v>
+        <v>16388</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>9167</v>
+        <v>9489</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>638</v>
+        <v>1272</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>28364</v>
+        <v>34006</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>29755</v>
+        <v>30944</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>5948</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="27">
@@ -2578,31 +2578,31 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>21538</v>
+        <v>27136</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>29542</v>
+        <v>30494</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>11167</v>
+        <v>12228</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>24191</v>
+        <v>27603</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>19925</v>
+        <v>19278</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>5517</v>
+        <v>6912</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>43237</v>
+        <v>50360</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>45515</v>
+        <v>47146</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>14615</v>
+        <v>16363</v>
       </c>
     </row>
     <row r="28">
@@ -2617,31 +2617,31 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>39</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -2652,31 +2652,31 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>61249</v>
+        <v>66211</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>36958</v>
+        <v>45813</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>29581</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>41330</v>
+        <v>46383</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23871</v>
+        <v>29364</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>15039</v>
+        <v>17426</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>102579</v>
+        <v>112594</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>60830</v>
+        <v>75177</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>44620</v>
+        <v>47007</v>
       </c>
     </row>
     <row r="30">
@@ -2687,31 +2687,31 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>52798</v>
+        <v>57306</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>28973</v>
+        <v>37400</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>22807</v>
+        <v>22601</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>33249</v>
+        <v>38484</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>17800</v>
+        <v>21756</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>9839</v>
+        <v>12695</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>90677</v>
+        <v>101831</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>50429</v>
+        <v>62591</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>35002</v>
+        <v>38165</v>
       </c>
     </row>
     <row r="31">
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>68741</v>
+        <v>75143</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>44420</v>
+        <v>55675</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>36842</v>
+        <v>37241</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>49928</v>
+        <v>55574</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>30733</v>
+        <v>37830</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>20768</v>
+        <v>23678</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>114133</v>
+        <v>125741</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>71562</v>
+        <v>86579</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>53006</v>
+        <v>56318</v>
       </c>
     </row>
     <row r="32">
@@ -2761,31 +2761,31 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>39</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>70251</v>
+        <v>78489</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>61574</v>
+        <v>72666</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>31027</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>60371</v>
+        <v>69288</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>47741</v>
+        <v>51848</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>10503</v>
+        <v>11822</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>130622</v>
+        <v>147777</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>109315</v>
+        <v>124513</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>41530</v>
+        <v>42849</v>
       </c>
     </row>
     <row r="34">
@@ -2831,31 +2831,31 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>61718</v>
+        <v>68677</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>53551</v>
+        <v>63406</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>22990</v>
+        <v>23364</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>50816</v>
+        <v>59796</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>40097</v>
+        <v>43185</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>6163</v>
+        <v>6970</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>117507</v>
+        <v>134314</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>98306</v>
+        <v>110829</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>32504</v>
+        <v>33415</v>
       </c>
     </row>
     <row r="35">
@@ -2866,31 +2866,31 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>78682</v>
+        <v>87725</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>72383</v>
+        <v>82298</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>38685</v>
+        <v>39312</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>68650</v>
+        <v>79095</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>56206</v>
+        <v>61479</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>16362</v>
+        <v>17266</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>142448</v>
+        <v>162191</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>123207</v>
+        <v>137506</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>51263</v>
+        <v>52257</v>
       </c>
     </row>
     <row r="36">
@@ -2905,31 +2905,31 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37">
@@ -2940,31 +2940,31 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
     </row>
     <row r="38">
@@ -2975,31 +2975,31 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
     </row>
     <row r="39">
@@ -3010,31 +3010,31 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
     </row>
     <row r="40">
